--- a/data/Пути.xlsx
+++ b/data/Пути.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30cfed6937883564/Документы/Education/GetData/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d_ternovoy\Desktop\Обучение\GetDataNew\GetDataScript\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{3C8B8ECC-CCF6-46D6-9F37-E55B2139F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC8ECF9E-DC9A-4529-A055-9F8FBCACE458}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A92D269-6E05-4133-8C01-ABB50990414B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Пути" sheetId="5" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,18 +38,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>FilePath</t>
   </si>
   <si>
-    <t>C:\Users\denis\OneDrive\Документы\Education\GetData\source\Рабочий журнал_ ФХ_ЧМПЗ Москва.xlsm</t>
-  </si>
-  <si>
-    <t>C:\Users\denis\OneDrive\Документы\Education\GetData\source\КЦБ СЕРОЛОГ 2025.xlsm</t>
-  </si>
-  <si>
-    <t>C:\Users\denis\OneDrive\Документы\Education\GetData\source\МСП СЕРОЛОГИЯ.xlsm</t>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Липецк\КЦЛ Микробиология 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Брянск\Журнал 2025\КЦБ МКБ 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Брянск\Журнал 2025\КЦБ СЕРОЛОГ 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Лиско Бройлер\2025\ЛБ Микробиология рабочий журнал СЕНТЯБРЬ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ЧМПЗ Пенза\2025_Журналы регистрации ПЕН\ПЕН МБ Рабочий журнал с формулам.январь-июнь, 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Моссельпром\2025 год\МСП МБ-3кварт.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ООО УМК\МБ журнал УБР 07-09.25.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Отечественный Продукт\Отечественный продукт микробиология рабочий журнал июль-сентябрь 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ПИТ\Журналы ПИТ 2023\Рабочий журнал_МБ -07-09.2025г.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ПИТ\Журналы ПИТ 2023\Рабочий журнал_ФХ_ГОРЕЛОВО -07-09.2025г.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ПИТ\Журналы ПИТ 2023\Рабочий журнал_ФХ_СИНЯВИНО - 07-09.2025г.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ЧМПЗ\Рабочий журнал_ МБ_ЧМПЗ Москва.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ЧМПЗ\Рабочий журнал_ФХ_ЧМПЗ Москва.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Алтайский Бройлер\2025\АБ МБ ВЫРАЩ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Алтайский Бройлер\2025\АБ МБ ППК.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Алтайский Бройлер\2025\АБ СЕР.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Алтайский Бройлер\2025\АБ ФХ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Бройлер Инвест\2025\Шаблон рабочего журнала БИ по серологии.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ВПФ\2025\ВПФ журнал МБ 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ВПФ\2025\ВПФ журнал СЕР 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Липецк\КЦЛ Серология 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Тула\2025 год\КЦ Тула МБ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\КЦ Тула\2025 год\КЦ Тула Серология.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Лиско Бройлер\2025\ЛБ Паразитология рабочий журнал 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Лиско Бройлер\2025\Серология рабочего журнала с формулами.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Лиско Бройлер\2025\ЛБ ФХ рабочий журнал 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Моссельпром\2025 год\МСП СЕРОЛОГИЯ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\Моссельпром\2025 год\МСП Физ.Химия .xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ООО УМК\Копия Серология  журнал 2025 г.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ТБ\МБ\2025\рабочий журнал с формулами ТБ 2025 Год.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ТБ\Серология\Рабочий журнал серология ТБ 2025г\рабочий журнал серология ТБ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ТБ\Физхимия\2024\ФХ рабочий журнал с формулами ТБ.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\ЧМПЗ Пенза\2025_Журналы регистрации ПЕН\ПЕН ФХ рабочий журнал 2025.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\РУСКОМ\РУСКОМ журнал СЕР.xlsm</t>
+  </si>
+  <si>
+    <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\РУСКОМ\МБ РУСКОМ.xlsm</t>
   </si>
 </sst>
 </file>
@@ -84,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,11 +189,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -104,14 +231,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -120,6 +251,31 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -156,10 +312,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BEDF317-EEB6-4008-989B-0DC66CEEE70F}" name="Пути" displayName="Пути" ref="A1:A4" headerRowDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BEDF317-EEB6-4008-989B-0DC66CEEE70F}" name="Пути" displayName="Пути" ref="A1:A4" headerRowDxfId="3" dataDxfId="0" tableBorderDxfId="2">
   <autoFilter ref="A1:A4" xr:uid="{A880B96C-3C94-4183-B1C4-FD37A7F9CB8E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{22589EB5-2FB4-4120-8F62-3F36EE03861C}" name="FilePath" totalsRowLabel="Итог" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{22589EB5-2FB4-4120-8F62-3F36EE03861C}" name="FilePath" totalsRowLabel="Итог" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -429,28 +585,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DFF35E-5C33-498E-9F2F-57467A430D1B}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="217.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="217.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -462,4 +618,189 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DB77CE-37A5-439E-B6FF-8FAAE2170D2A}">
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Пути.xlsx
+++ b/data/Пути.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d_ternovoy\Desktop\Обучение\GetDataNew\GetDataScript\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30cfed6937883564/Документы/Education/GetData/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A92D269-6E05-4133-8C01-ABB50990414B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8A92D269-6E05-4133-8C01-ABB50990414B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7A3C90-F149-4569-ACF5-D0B88AE33C73}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Пути" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>FilePath</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>N:\Дирекция по управлению качеством\Документация локальных лабораторий\Рабочие журналы\Журналы регистрации\РУСКОМ\МБ РУСКОМ.xlsm</t>
+  </si>
+  <si>
+    <t>C:\Users\denis\OneDrive\Документы\Education\GetData\source\МСП СЕРОЛОГИЯ.xlsm</t>
   </si>
 </sst>
 </file>
@@ -251,15 +254,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="1"/>
@@ -283,6 +277,15 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -312,10 +315,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BEDF317-EEB6-4008-989B-0DC66CEEE70F}" name="Пути" displayName="Пути" ref="A1:A4" headerRowDxfId="3" dataDxfId="0" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BEDF317-EEB6-4008-989B-0DC66CEEE70F}" name="Пути" displayName="Пути" ref="A1:A4" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="A1:A4" xr:uid="{A880B96C-3C94-4183-B1C4-FD37A7F9CB8E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{22589EB5-2FB4-4120-8F62-3F36EE03861C}" name="FilePath" totalsRowLabel="Итог" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{22589EB5-2FB4-4120-8F62-3F36EE03861C}" name="FilePath" totalsRowLabel="Итог" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -585,27 +588,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DFF35E-5C33-498E-9F2F-57467A430D1B}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="217.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="217.36328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -623,179 +626,179 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DB77CE-37A5-439E-B6FF-8FAAE2170D2A}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
